--- a/data/trans_bre/IP25-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Habitat-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-2,05%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 7,64</t>
+          <t>-3,86; 6,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,79</t>
+          <t>-4,07; 6,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,0</t>
+          <t>-8,14; 4,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,19; 8,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 9,01</t>
+          <t>-4,36; 6,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 6,58</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-7,93; 4,57</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-8,63; 4,72</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>-1,02%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,72</t>
+          <t>-3,73; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,85</t>
+          <t>-4,47; 4,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,26</t>
+          <t>-4,94; 3,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,1; 8,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 7,95</t>
+          <t>-4,8; 5,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 5,59</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-5,72; 3,67</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,28; 4,05</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>-6,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>-1,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 6,5</t>
+          <t>-5,31; 5,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -0,32</t>
+          <t>-12,39; 0,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 2,44</t>
+          <t>-5,61; 2,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,92; 6,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 7,72</t>
+          <t>-13,29; 0,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,79; -0,4</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 2,61</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,89; 2,39</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>-4,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-1,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 11,31</t>
+          <t>1,31; 10,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 0,54</t>
+          <t>-8,11; 0,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,65</t>
+          <t>-7,2; 3,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,49; 12,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 13,64</t>
+          <t>-8,59; 1,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 0,57</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 4,23</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-7,96; 3,95</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>-2,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>-1,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 5,65</t>
+          <t>0,28; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,5</t>
+          <t>-4,65; 0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,09</t>
+          <t>-4,04; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,23; 6,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 6,52</t>
+          <t>-4,98; 0,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,39; 1,03</t>
         </is>
       </c>
     </row>
@@ -1108,12 +992,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
   </mergeCells>

--- a/data/trans_bre/IP25-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,99</t>
+          <t>-4,06; 7,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 6,05</t>
+          <t>-3,87; 6,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 4,19</t>
+          <t>-7,46; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 8,1</t>
+          <t>-4,45; 8,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 6,88</t>
+          <t>-4,17; 6,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 4,72</t>
+          <t>-7,98; 4,36</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 7,03</t>
+          <t>-3,79; 6,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 4,7</t>
+          <t>-4,71; 4,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,59</t>
+          <t>-5,09; 3,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 8,48</t>
+          <t>-4,23; 7,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 5,31</t>
+          <t>-5,09; 5,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 4,05</t>
+          <t>-5,48; 3,61</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,64</t>
+          <t>-5,33; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 0,21</t>
+          <t>-11,92; -0,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,23</t>
+          <t>-5,38; 2,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 6,63</t>
+          <t>-5,81; 7,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 0,21</t>
+          <t>-12,87; -0,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 2,39</t>
+          <t>-5,62; 2,4</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 10,74</t>
+          <t>1,14; 10,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 0,94</t>
+          <t>-8,69; 0,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 3,42</t>
+          <t>-6,4; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,72</t>
+          <t>1,26; 13,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 1,02</t>
+          <t>-9,15; 0,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 3,95</t>
+          <t>-7,12; 4,65</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,5</t>
+          <t>0,24; 5,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,54</t>
+          <t>-4,63; 0,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,93</t>
+          <t>-3,92; 1,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,4</t>
+          <t>0,31; 6,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,6</t>
+          <t>-5,01; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,03</t>
+          <t>-4,27; 1,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 7,29</t>
+          <t>-3,71; 7,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 6,17</t>
+          <t>-3,97; 5,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 3,92</t>
+          <t>-7,39; 4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 8,52</t>
+          <t>-3,96; 9,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 6,92</t>
+          <t>-4,28; 6,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 4,36</t>
+          <t>-7,93; 4,57</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 6,5</t>
+          <t>-3,35; 6,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,67</t>
+          <t>-4,46; 4,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 3,14</t>
+          <t>-5,36; 3,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 7,67</t>
+          <t>-3,72; 7,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 5,34</t>
+          <t>-4,94; 5,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 3,61</t>
+          <t>-5,72; 3,67</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 6,17</t>
+          <t>-5,6; 6,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,92; -0,15</t>
+          <t>-11,73; -0,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,26</t>
+          <t>-5,79; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,23</t>
+          <t>-6,1; 7,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,87; -0,21</t>
+          <t>-12,79; -0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 2,4</t>
+          <t>-5,97; 2,61</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,96</t>
+          <t>1,47; 11,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 0,62</t>
+          <t>-9,56; 0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 4,06</t>
+          <t>-6,63; 3,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,19</t>
+          <t>1,69; 13,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 0,68</t>
+          <t>-10,17; 0,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 4,65</t>
+          <t>-7,17; 4,23</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 5,55</t>
+          <t>0,09; 5,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,41</t>
+          <t>-4,72; 0,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,03</t>
+          <t>-3,84; 1,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,48</t>
+          <t>0,1; 6,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,44</t>
+          <t>-5,12; 0,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,15</t>
+          <t>-4,17; 1,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,05%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.822785831232565</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.106053613357705</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.873831068274312</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.02045282631707227</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.01206979019601897</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.02050780277737375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,71; 7,64</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,97; 5,79</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,39; 4,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,96; 9,01</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-4,28; 6,58</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,93; 4,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.711684330192267</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.968204298001534</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.394376934522641</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.03956089335020425</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.04281692198937182</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.0792957393044126</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7.63996035085859</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.785113577536893</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.002098628419676</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.09005199402538445</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.06575208691918337</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.045681334477328</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,35; 6,72</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,46; 4,85</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,36; 3,26</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,72; 7,95</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 5,59</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,72; 3,67</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.606120499353281</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1152717053570562</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.9325145825192616</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.01850843911420173</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.001274108601325076</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01021990214409536</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-5,99</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-6,61%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,73%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.354964485857695</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.458545326121942</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.355385633314016</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.03721575478934133</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.04936596941453907</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05720066035207295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,6; 6,5</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,73; -0,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,79; 2,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,1; 7,72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-12,79; -0,4</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 2,61</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.720390693156022</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.851426953638139</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.258383968400683</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.07946192663610635</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.0559199157709564</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03666622424598203</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +767,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,84</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,16%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-1,69%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.4682459882846657</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-5.987201132455711</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.643016078628823</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.005304269197277491</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.06614980591284657</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.0173065040598005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 11,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-9,56; 0,54</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,63; 3,65</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,69; 13,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-10,17; 0,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-7,17; 4,23</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.60457390286076</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.73103167742352</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.794026808156729</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.06095872980985911</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1279227535032244</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.05973595940119169</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.498628842554159</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.3213471068155063</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.443398385709852</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.07721558488324998</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-0.003967883790354038</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.02605905059008296</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.126399586412989</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.840518751529642</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.49052485478709</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.07073440036640626</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.04156291329171089</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.01685241995588837</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.469000864154793</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-9.564760638883092</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.627577342298288</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.01685512373796881</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1016861863404863</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.07165665613918171</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11.3050038706114</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5415439392044381</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.651728056051804</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1364172141544586</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.005719941636794977</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.04230885746679326</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,17</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 5,65</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,72; 0,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 1,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 6,52</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 0,55</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 1,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.776740117313381</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.173199715805918</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.493617665982028</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.03172082477166212</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02381458875773705</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01635533306248851</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.08915016252287135</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.719499292334402</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.836271919237275</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0.0009667227748420159</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05121490315252061</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04166839330405903</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.647938539766834</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4989331690560716</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.086920194524964</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.06523975511321876</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.005458926872619372</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.01207351016952813</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1012,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
